--- a/单刷2023B/result1.xlsx
+++ b/单刷2023B/result1.xlsx
@@ -549,38 +549,32 @@
           <t>覆盖宽度/m</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>315.60</t>
-        </is>
+      <c r="B3" s="1" t="n">
+        <v>315.71</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>297.41</v>
+        <v>297.53</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>279.23</v>
+        <v>279.35</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>261.08</v>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>242.90</t>
-        </is>
+        <v>261.17</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>242.99</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>224.72</v>
+        <v>224.81</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>206.57</v>
+        <v>206.63</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>188.39</v>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>170.20</t>
-        </is>
+        <v>188.45</v>
+      </c>
+      <c r="J3" s="1" t="n">
+        <v>170.27</v>
       </c>
     </row>
     <row r="4" ht="39.75" customHeight="1">
@@ -596,37 +590,37 @@
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>36.63%</t>
+          <t>36.65%</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>32.75%</t>
+          <t>32.78%</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>28.37%</t>
+          <t>28.40%</t>
         </is>
       </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
-          <t>23.40%</t>
+          <t>23.42%</t>
         </is>
       </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
-          <t>17.66%</t>
+          <t>17.69%</t>
         </is>
       </c>
       <c r="H4" s="1" t="inlineStr">
         <is>
-          <t>11.00%</t>
+          <t>11.03%</t>
         </is>
       </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
-          <t>3.18%</t>
+          <t>3.21%</t>
         </is>
       </c>
       <c r="J4" s="1" t="inlineStr">

--- a/单刷2023B/result1.xlsx
+++ b/单刷2023B/result1.xlsx
@@ -590,37 +590,37 @@
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>36.65%</t>
+          <t>32.78%</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>32.78%</t>
+          <t>28.40%</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>28.40%</t>
+          <t>23.42%</t>
         </is>
       </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
-          <t>23.42%</t>
+          <t>17.69%</t>
         </is>
       </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
-          <t>17.69%</t>
+          <t>11.03%</t>
         </is>
       </c>
       <c r="H4" s="1" t="inlineStr">
         <is>
-          <t>11.03%</t>
+          <t>3.21%</t>
         </is>
       </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>无重叠</t>
         </is>
       </c>
       <c r="J4" s="1" t="inlineStr">
